--- a/nriss-patch-2/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4545" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:58:47+00:00</t>
+    <t>2026-08-04T07:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1450,9 +1450,6 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis|202606190000</t>
-  </si>
-  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -1622,40 +1619,11 @@
     <t>Task.input:natureTransport.type</t>
   </si>
   <si>
-    <t>Task.input:natureTransport.type.id</t>
-  </si>
-  <si>
-    <t>Task.input:natureTransport.type.extension</t>
-  </si>
-  <si>
-    <t>Task.input:natureTransport.type.coding</t>
-  </si>
-  <si>
-    <t>Task.input:natureTransport.type.coding.id</t>
-  </si>
-  <si>
-    <t>Task.input:natureTransport.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Task.input:natureTransport.type.coding.system</t>
-  </si>
-  <si>
-    <t>Task.input:natureTransport.type.coding.version</t>
-  </si>
-  <si>
-    <t>Task.input:natureTransport.type.coding.code</t>
-  </si>
-  <si>
-    <t>GEN-345</t>
-  </si>
-  <si>
-    <t>Task.input:natureTransport.type.coding.display</t>
-  </si>
-  <si>
-    <t>Task.input:natureTransport.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Task.input:natureTransport.type.text</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="GEN-345"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Task.input:natureTransport.value[x]</t>
@@ -2141,7 +2109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN125"/>
+  <dimension ref="A1:AN114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.40625" customWidth="true" bestFit="true"/>
@@ -9660,29 +9628,31 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9700,21 +9670,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>464</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9740,13 +9710,13 @@
         <v>233</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9796,7 +9766,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9814,21 +9784,21 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>472</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9854,14 +9824,14 @@
         <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9871,46 +9841,46 @@
         <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9928,21 +9898,21 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9968,14 +9938,14 @@
         <v>233</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -10024,7 +9994,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10042,21 +10012,21 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10079,19 +10049,19 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10140,7 +10110,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10158,21 +10128,21 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>499</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10198,16 +10168,16 @@
         <v>233</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10256,7 +10226,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10274,18 +10244,18 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>508</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>426</v>
@@ -10348,7 +10318,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10395,13 +10365,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>409</v>
@@ -10426,7 +10396,7 @@
         <v>379</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>412</v>
@@ -10511,7 +10481,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>416</v>
@@ -10623,7 +10593,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>417</v>
@@ -10737,7 +10707,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>418</v>
@@ -10853,7 +10823,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>419</v>
@@ -10901,7 +10871,7 @@
         <v>77</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>77</v>
+        <v>517</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>77</v>
@@ -10972,7 +10942,7 @@
         <v>518</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10980,7 +10950,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>87</v>
@@ -10995,13 +10965,13 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>267</v>
+        <v>428</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>268</v>
+        <v>429</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11052,10 +11022,10 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>269</v>
+        <v>426</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>87</v>
@@ -11064,13 +11034,13 @@
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>270</v>
+        <v>415</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11084,18 +11054,20 @@
         <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="D79" t="s" s="2">
-        <v>132</v>
+        <v>409</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -11107,18 +11079,18 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>133</v>
+        <v>379</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>134</v>
+        <v>411</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -11154,19 +11126,19 @@
         <v>77</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>276</v>
+        <v>408</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11178,13 +11150,13 @@
         <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>270</v>
+        <v>415</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -11195,10 +11167,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11209,7 +11181,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
@@ -11218,23 +11190,19 @@
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>443</v>
+        <v>233</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>444</v>
+        <v>267</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
       </c>
@@ -11282,50 +11250,50 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>448</v>
+        <v>269</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>449</v>
+        <v>270</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>450</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>452</v>
+        <v>417</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>77</v>
@@ -11337,15 +11305,17 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11394,19 +11364,19 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -11423,14 +11393,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>454</v>
+        <v>418</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11443,24 +11413,26 @@
         <v>77</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>272</v>
+        <v>389</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -11496,19 +11468,19 @@
         <v>77</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>276</v>
+        <v>390</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11526,7 +11498,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11537,18 +11509,18 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>87</v>
@@ -11560,22 +11532,22 @@
         <v>77</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>101</v>
+        <v>192</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>458</v>
+        <v>422</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>459</v>
+        <v>423</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>460</v>
+        <v>424</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -11600,11 +11572,13 @@
         <v>77</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>461</v>
+        <v>77</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>77</v>
@@ -11622,10 +11596,10 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>462</v>
+        <v>419</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>87</v>
@@ -11640,21 +11614,21 @@
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>463</v>
+        <v>415</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>464</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>466</v>
+        <v>438</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11674,20 +11648,18 @@
         <v>77</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>233</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>467</v>
+        <v>267</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11736,7 +11708,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>470</v>
+        <v>269</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11748,38 +11720,38 @@
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>471</v>
+        <v>270</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>472</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>77</v>
@@ -11788,21 +11760,21 @@
         <v>77</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>475</v>
+        <v>134</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>77</v>
       </c>
@@ -11811,7 +11783,7 @@
         <v>77</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>526</v>
+        <v>77</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>77</v>
@@ -11838,43 +11810,43 @@
         <v>77</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>479</v>
+        <v>276</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>480</v>
+        <v>270</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" hidden="true">
@@ -11882,7 +11854,7 @@
         <v>527</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>483</v>
+        <v>442</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11893,7 +11865,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>77</v>
@@ -11905,17 +11877,19 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>233</v>
+        <v>443</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>484</v>
+        <v>444</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O86" t="s" s="2">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -11964,13 +11938,13 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>487</v>
+        <v>448</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>77</v>
@@ -11982,13 +11956,13 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>489</v>
+        <v>450</v>
       </c>
     </row>
     <row r="87" hidden="true">
@@ -11996,7 +11970,7 @@
         <v>528</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12019,19 +11993,19 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>492</v>
+        <v>233</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>77</v>
@@ -12041,7 +12015,7 @@
         <v>77</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>77</v>
+        <v>529</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>77</v>
@@ -12080,7 +12054,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12098,21 +12072,21 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>501</v>
+        <v>426</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12120,7 +12094,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>87</v>
@@ -12132,23 +12106,19 @@
         <v>77</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>233</v>
+        <v>531</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>502</v>
+        <v>428</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>77</v>
       </c>
@@ -12196,10 +12166,10 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>506</v>
+        <v>426</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>87</v>
@@ -12214,29 +12184,31 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>507</v>
+        <v>415</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>508</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="D89" t="s" s="2">
-        <v>77</v>
+        <v>409</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>87</v>
@@ -12251,16 +12223,18 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>192</v>
+        <v>379</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>428</v>
+        <v>534</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
       </c>
@@ -12308,13 +12282,13 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>77</v>
@@ -12337,16 +12311,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12365,18 +12337,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>379</v>
+        <v>233</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>411</v>
+        <v>267</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>77</v>
       </c>
@@ -12424,25 +12394,25 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>408</v>
+        <v>269</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -12453,21 +12423,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>77</v>
@@ -12479,15 +12449,17 @@
         <v>77</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -12536,19 +12508,19 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
@@ -12565,14 +12537,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12585,24 +12557,26 @@
         <v>77</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>272</v>
+        <v>389</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
       </c>
@@ -12650,7 +12624,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>276</v>
+        <v>390</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12668,7 +12642,7 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -12679,45 +12653,45 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>136</v>
+        <v>423</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>142</v>
+        <v>424</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -12742,10 +12716,10 @@
         <v>77</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="Z93" t="s" s="2">
         <v>77</v>
@@ -12766,25 +12740,25 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>130</v>
+        <v>415</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -12795,18 +12769,18 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>420</v>
+        <v>77</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>87</v>
@@ -12821,20 +12795,16 @@
         <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>421</v>
+        <v>267</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>77</v>
       </c>
@@ -12858,10 +12828,10 @@
         <v>77</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Z94" t="s" s="2">
         <v>77</v>
@@ -12882,10 +12852,10 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>419</v>
+        <v>269</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>87</v>
@@ -12894,13 +12864,13 @@
         <v>77</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -12911,21 +12881,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>77</v>
@@ -12937,15 +12907,17 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -12982,31 +12954,31 @@
         <v>77</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>77</v>
@@ -13023,14 +12995,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13046,21 +13018,23 @@
         <v>77</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>133</v>
+        <v>443</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>134</v>
+        <v>444</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>272</v>
+        <v>445</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>77</v>
       </c>
@@ -13096,19 +13070,19 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>276</v>
+        <v>448</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13120,27 +13094,27 @@
         <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>270</v>
+        <v>449</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>77</v>
+        <v>450</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>442</v>
+        <v>500</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13151,7 +13125,7 @@
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>77</v>
@@ -13163,19 +13137,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>443</v>
+        <v>233</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>444</v>
+        <v>501</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>445</v>
+        <v>502</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>447</v>
+        <v>504</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13185,7 +13159,7 @@
         <v>77</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>77</v>
+        <v>543</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>77</v>
@@ -13224,13 +13198,13 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>448</v>
+        <v>505</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>77</v>
@@ -13242,21 +13216,21 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>449</v>
+        <v>506</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>450</v>
+        <v>507</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>501</v>
+        <v>426</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13264,7 +13238,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>87</v>
@@ -13276,23 +13250,19 @@
         <v>77</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>233</v>
+        <v>531</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>502</v>
+        <v>428</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
       </c>
@@ -13301,7 +13271,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>541</v>
+        <v>77</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13340,10 +13310,10 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>506</v>
+        <v>426</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>87</v>
@@ -13358,32 +13328,34 @@
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>507</v>
+        <v>415</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>508</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C99" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="D99" t="s" s="2">
-        <v>77</v>
+        <v>409</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>77</v>
@@ -13395,16 +13367,18 @@
         <v>77</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>543</v>
+        <v>379</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>428</v>
+        <v>547</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>77</v>
       </c>
@@ -13452,13 +13426,13 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>77</v>
@@ -13481,16 +13455,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -13509,18 +13481,16 @@
         <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>379</v>
+        <v>233</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>546</v>
+        <v>267</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="N100" s="2"/>
-      <c r="O100" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>77</v>
       </c>
@@ -13568,25 +13538,25 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>408</v>
+        <v>269</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
@@ -13597,21 +13567,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>77</v>
@@ -13623,15 +13593,17 @@
         <v>77</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -13680,19 +13652,19 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>77</v>
@@ -13709,14 +13681,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -13729,24 +13701,26 @@
         <v>77</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>272</v>
+        <v>389</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
       </c>
@@ -13794,7 +13768,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>276</v>
+        <v>390</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13812,7 +13786,7 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -13823,45 +13797,45 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>136</v>
+        <v>423</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>142</v>
+        <v>424</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13886,10 +13860,10 @@
         <v>77</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="Z103" t="s" s="2">
         <v>77</v>
@@ -13910,25 +13884,25 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>130</v>
+        <v>415</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
@@ -13939,18 +13913,18 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>420</v>
+        <v>77</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>87</v>
@@ -13965,20 +13939,16 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>421</v>
+        <v>267</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>77</v>
       </c>
@@ -14002,10 +13972,10 @@
         <v>77</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Z104" t="s" s="2">
         <v>77</v>
@@ -14026,10 +13996,10 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>419</v>
+        <v>269</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>87</v>
@@ -14038,13 +14008,13 @@
         <v>77</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -14055,21 +14025,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>77</v>
@@ -14081,15 +14051,17 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14126,31 +14098,31 @@
         <v>77</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>77</v>
@@ -14167,14 +14139,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14190,21 +14162,23 @@
         <v>77</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>133</v>
+        <v>443</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>134</v>
+        <v>444</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>272</v>
+        <v>445</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O106" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>77</v>
       </c>
@@ -14240,19 +14214,19 @@
         <v>77</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>276</v>
+        <v>448</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14264,27 +14238,27 @@
         <v>77</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>270</v>
+        <v>449</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>77</v>
+        <v>450</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>442</v>
+        <v>500</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14295,7 +14269,7 @@
         <v>78</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>77</v>
@@ -14307,19 +14281,19 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>443</v>
+        <v>233</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>444</v>
+        <v>501</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>445</v>
+        <v>502</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>447</v>
+        <v>504</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -14329,7 +14303,7 @@
         <v>77</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>77</v>
+        <v>556</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>77</v>
@@ -14368,13 +14342,13 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>448</v>
+        <v>505</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>77</v>
@@ -14386,21 +14360,21 @@
         <v>77</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>449</v>
+        <v>506</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>450</v>
+        <v>507</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>501</v>
+        <v>426</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14408,7 +14382,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>87</v>
@@ -14420,23 +14394,19 @@
         <v>77</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>233</v>
+        <v>427</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>502</v>
+        <v>428</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>77</v>
       </c>
@@ -14445,7 +14415,7 @@
         <v>77</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>555</v>
+        <v>77</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>77</v>
@@ -14484,10 +14454,10 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>506</v>
+        <v>426</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>87</v>
@@ -14502,21 +14472,21 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>507</v>
+        <v>415</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>508</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>426</v>
+        <v>558</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14524,10 +14494,10 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>77</v>
@@ -14539,16 +14509,18 @@
         <v>77</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>543</v>
+        <v>379</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>428</v>
+        <v>559</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>429</v>
+        <v>560</v>
       </c>
       <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>77</v>
       </c>
@@ -14596,13 +14568,13 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>426</v>
+        <v>558</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>77</v>
@@ -14625,23 +14597,21 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>77</v>
@@ -14653,18 +14623,16 @@
         <v>77</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>379</v>
+        <v>233</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>559</v>
+        <v>267</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="N110" s="2"/>
-      <c r="O110" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>77</v>
       </c>
@@ -14712,25 +14680,25 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>408</v>
+        <v>269</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
@@ -14741,21 +14709,21 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>416</v>
+        <v>563</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>77</v>
@@ -14767,15 +14735,17 @@
         <v>77</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -14824,19 +14794,19 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>77</v>
@@ -14853,14 +14823,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>417</v>
+        <v>564</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -14873,24 +14843,26 @@
         <v>77</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>272</v>
+        <v>389</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O112" s="2"/>
+      <c r="O112" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>77</v>
       </c>
@@ -14938,7 +14910,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>276</v>
+        <v>390</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14956,7 +14928,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14967,45 +14939,43 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>418</v>
+        <v>565</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>388</v>
+        <v>566</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>142</v>
+        <v>568</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -15030,10 +15000,10 @@
         <v>77</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>77</v>
+        <v>569</v>
       </c>
       <c r="Z113" t="s" s="2">
         <v>77</v>
@@ -15054,25 +15024,25 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>390</v>
+        <v>565</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>130</v>
+        <v>415</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -15083,14 +15053,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>419</v>
+        <v>570</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>420</v>
+        <v>77</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15109,19 +15079,17 @@
         <v>77</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>192</v>
+        <v>427</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>421</v>
+        <v>571</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>424</v>
+        <v>573</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>77</v>
@@ -15146,10 +15114,10 @@
         <v>77</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Z114" t="s" s="2">
         <v>77</v>
@@ -15170,7 +15138,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>419</v>
+        <v>570</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>87</v>
@@ -15197,1262 +15165,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="P120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="P124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN125">
+  <autoFilter ref="A1:AN114">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16462,7 +15176,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI124">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nriss-patch-2/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$103</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3751" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:44:41+00:00</t>
+    <t>2026-08-07T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1377,219 +1377,11 @@
     <t>Task.input:typeMotorisation.type</t>
   </si>
   <si>
-    <t>Task.input:typeMotorisation.type.id</t>
-  </si>
-  <si>
-    <t>Task.input.type.id</t>
-  </si>
-  <si>
-    <t>Task.input:typeMotorisation.type.extension</t>
-  </si>
-  <si>
-    <t>Task.input.type.extension</t>
-  </si>
-  <si>
-    <t>Task.input:typeMotorisation.type.coding</t>
-  </si>
-  <si>
-    <t>Task.input.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Task.input:typeMotorisation.type.coding.id</t>
-  </si>
-  <si>
-    <t>Task.input.type.coding.id</t>
-  </si>
-  <si>
-    <t>Task.input:typeMotorisation.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Task.input.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Task.input:typeMotorisation.type.coding.system</t>
-  </si>
-  <si>
-    <t>Task.input.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Task.input:typeMotorisation.type.coding.version</t>
-  </si>
-  <si>
-    <t>Task.input.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Task.input:typeMotorisation.type.coding.code</t>
-  </si>
-  <si>
-    <t>Task.input.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>GEN-346</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Task.input:typeMotorisation.type.coding.display</t>
-  </si>
-  <si>
-    <t>Task.input.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Task.input:typeMotorisation.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Task.input.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Task.input:typeMotorisation.type.text</t>
-  </si>
-  <si>
-    <t>Task.input.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="GEN-346"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Task.input:typeMotorisation.value[x]</t>
@@ -1650,16 +1442,74 @@
     <t>Task.input:lieuDepart.type.id</t>
   </si>
   <si>
+    <t>Task.input.type.id</t>
+  </si>
+  <si>
     <t>Task.input:lieuDepart.type.extension</t>
   </si>
   <si>
+    <t>Task.input.type.extension</t>
+  </si>
+  <si>
     <t>Task.input:lieuDepart.type.coding</t>
   </si>
   <si>
+    <t>Task.input.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
     <t>Task.input:lieuDepart.type.text</t>
   </si>
   <si>
+    <t>Task.input.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
     <t>Lieu de départ</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Task.input:lieuDepart.value[x]</t>
@@ -2109,11 +1959,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN114"/>
+  <dimension ref="A1:AN103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.40625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="29.59765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="37.6484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="27.80078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.17578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -8929,7 +8779,7 @@
         <v>77</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>77</v>
@@ -8997,10 +8847,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9008,7 +8858,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>87</v>
@@ -9023,13 +8873,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>267</v>
+        <v>428</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>268</v>
+        <v>429</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9056,13 +8906,11 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>77</v>
+        <v>439</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -9080,10 +8928,10 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>269</v>
+        <v>426</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>87</v>
@@ -9092,13 +8940,13 @@
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>270</v>
+        <v>415</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -9109,21 +8957,23 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="D62" t="s" s="2">
-        <v>132</v>
+        <v>409</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -9135,18 +8985,18 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>133</v>
+        <v>379</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>134</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
@@ -9182,19 +9032,19 @@
         <v>77</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>276</v>
+        <v>408</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9206,13 +9056,13 @@
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>270</v>
+        <v>415</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9223,10 +9073,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9237,7 +9087,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
@@ -9246,23 +9096,19 @@
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>443</v>
+        <v>233</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>444</v>
+        <v>267</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
@@ -9310,50 +9156,50 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>448</v>
+        <v>269</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>449</v>
+        <v>270</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>450</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>452</v>
+        <v>417</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9365,15 +9211,17 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9422,19 +9270,19 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
@@ -9451,14 +9299,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>454</v>
+        <v>418</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9471,24 +9319,26 @@
         <v>77</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>272</v>
+        <v>389</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9524,19 +9374,19 @@
         <v>77</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>276</v>
+        <v>390</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9554,7 +9404,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9565,18 +9415,18 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>87</v>
@@ -9588,22 +9438,22 @@
         <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>101</v>
+        <v>192</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>458</v>
+        <v>422</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>459</v>
+        <v>423</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>460</v>
+        <v>424</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9613,7 +9463,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>77</v>
+        <v>447</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -9628,10 +9478,10 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="Z66" t="s" s="2">
         <v>77</v>
@@ -9652,10 +9502,10 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>461</v>
+        <v>419</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>87</v>
@@ -9670,21 +9520,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>463</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>465</v>
+        <v>426</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9692,7 +9542,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>87</v>
@@ -9704,20 +9554,18 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>466</v>
+        <v>428</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9766,10 +9614,10 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>469</v>
+        <v>426</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>87</v>
@@ -9784,25 +9632,27 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>470</v>
+        <v>415</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>471</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>472</v>
+        <v>449</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="D68" t="s" s="2">
-        <v>77</v>
+        <v>409</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9818,20 +9668,20 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
+        <v>379</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>474</v>
+        <v>411</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>475</v>
+        <v>412</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>476</v>
+        <v>413</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9841,7 +9691,7 @@
         <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>477</v>
+        <v>77</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>77</v>
@@ -9880,13 +9730,13 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>478</v>
+        <v>408</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
@@ -9898,21 +9748,21 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>479</v>
+        <v>415</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>480</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>481</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>482</v>
+        <v>416</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9932,21 +9782,19 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>233</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>483</v>
+        <v>267</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>484</v>
+        <v>268</v>
       </c>
       <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>485</v>
-      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -9994,7 +9842,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>486</v>
+        <v>269</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10006,38 +9854,38 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>487</v>
+        <v>270</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>488</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>490</v>
+        <v>417</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -10046,23 +9894,21 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>491</v>
+        <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>492</v>
+        <v>134</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>493</v>
+        <v>272</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
       </c>
@@ -10110,74 +9956,74 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>496</v>
+        <v>276</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>497</v>
+        <v>270</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>498</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>499</v>
+        <v>453</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>500</v>
+        <v>418</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>77</v>
+        <v>387</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>501</v>
+        <v>388</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>502</v>
+        <v>389</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>503</v>
+        <v>136</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>504</v>
+        <v>142</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10226,43 +10072,43 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>505</v>
+        <v>390</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>507</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>454</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10284,13 +10130,17 @@
         <v>192</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
@@ -10314,11 +10164,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>509</v>
+        <v>77</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10336,7 +10188,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>87</v>
@@ -10365,20 +10217,18 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>510</v>
+        <v>455</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>511</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>87</v>
@@ -10393,18 +10243,16 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>379</v>
+        <v>233</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>512</v>
+        <v>267</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10452,25 +10300,25 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>408</v>
+        <v>269</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10481,21 +10329,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>513</v>
+        <v>457</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>416</v>
+        <v>458</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
@@ -10507,15 +10355,17 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10552,31 +10402,31 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
@@ -10593,14 +10443,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>514</v>
+        <v>459</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>417</v>
+        <v>460</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10616,21 +10466,23 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>133</v>
+        <v>461</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>134</v>
+        <v>462</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>272</v>
+        <v>463</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
       </c>
@@ -10678,7 +10530,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>276</v>
+        <v>466</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10690,62 +10542,62 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>270</v>
+        <v>467</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>77</v>
+        <v>468</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>515</v>
+        <v>469</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>418</v>
+        <v>470</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>387</v>
+        <v>77</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>133</v>
+        <v>233</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>388</v>
+        <v>471</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>389</v>
+        <v>472</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>136</v>
+        <v>473</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>142</v>
+        <v>474</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10755,7 +10607,7 @@
         <v>77</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>77</v>
+        <v>475</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>77</v>
@@ -10794,43 +10646,43 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>390</v>
+        <v>476</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>130</v>
+        <v>477</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>77</v>
+        <v>478</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>516</v>
+        <v>479</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>420</v>
+        <v>77</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10849,20 +10701,16 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>192</v>
+        <v>480</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
       </c>
@@ -10871,7 +10719,7 @@
         <v>77</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>517</v>
+        <v>77</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>77</v>
@@ -10886,10 +10734,10 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Z77" t="s" s="2">
         <v>77</v>
@@ -10910,7 +10758,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>87</v>
@@ -10939,18 +10787,20 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>518</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="D78" t="s" s="2">
-        <v>77</v>
+        <v>409</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>87</v>
@@ -10965,16 +10815,18 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>192</v>
+        <v>379</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>428</v>
+        <v>483</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
@@ -11022,13 +10874,13 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
@@ -11051,16 +10903,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>519</v>
+        <v>484</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11079,18 +10929,16 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>379</v>
+        <v>233</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>411</v>
+        <v>267</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -11138,25 +10986,25 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>408</v>
+        <v>269</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -11167,21 +11015,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>521</v>
+        <v>485</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
@@ -11193,15 +11041,17 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11250,19 +11100,19 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
@@ -11279,14 +11129,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>522</v>
+        <v>486</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11299,24 +11149,26 @@
         <v>77</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>272</v>
+        <v>389</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
@@ -11364,7 +11216,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>276</v>
+        <v>390</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11382,7 +11234,7 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -11393,45 +11245,45 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>523</v>
+        <v>487</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>136</v>
+        <v>423</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>142</v>
+        <v>424</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -11456,10 +11308,10 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="Z82" t="s" s="2">
         <v>77</v>
@@ -11480,25 +11332,25 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>130</v>
+        <v>415</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11509,18 +11361,18 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>524</v>
+        <v>488</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>420</v>
+        <v>77</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>87</v>
@@ -11535,20 +11387,16 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>421</v>
+        <v>267</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -11572,10 +11420,10 @@
         <v>77</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Z83" t="s" s="2">
         <v>77</v>
@@ -11596,10 +11444,10 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>419</v>
+        <v>269</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>87</v>
@@ -11608,13 +11456,13 @@
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -11625,21 +11473,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>525</v>
+        <v>489</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>77</v>
@@ -11651,15 +11499,17 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11696,31 +11546,31 @@
         <v>77</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -11737,14 +11587,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>526</v>
+        <v>490</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -11760,21 +11610,23 @@
         <v>77</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>133</v>
+        <v>461</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>134</v>
+        <v>462</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>272</v>
+        <v>463</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
       </c>
@@ -11810,19 +11662,19 @@
         <v>77</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>276</v>
+        <v>466</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11834,27 +11686,27 @@
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>270</v>
+        <v>467</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>77</v>
+        <v>468</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>527</v>
+        <v>491</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11865,7 +11717,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>77</v>
@@ -11877,19 +11729,19 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>443</v>
+        <v>233</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -11899,7 +11751,7 @@
         <v>77</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>77</v>
+        <v>492</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>77</v>
@@ -11938,13 +11790,13 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>77</v>
@@ -11956,21 +11808,21 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>450</v>
+        <v>478</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>528</v>
+        <v>493</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>500</v>
+        <v>426</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11978,7 +11830,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>87</v>
@@ -11990,23 +11842,19 @@
         <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>233</v>
+        <v>480</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>501</v>
+        <v>428</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>77</v>
       </c>
@@ -12015,7 +11863,7 @@
         <v>77</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>529</v>
+        <v>77</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>77</v>
@@ -12054,10 +11902,10 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>505</v>
+        <v>426</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>87</v>
@@ -12072,32 +11920,34 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>506</v>
+        <v>415</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>507</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>530</v>
+        <v>494</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="D88" t="s" s="2">
-        <v>77</v>
+        <v>409</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>77</v>
@@ -12109,16 +11959,18 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>531</v>
+        <v>379</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>428</v>
+        <v>496</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
       </c>
@@ -12166,13 +12018,13 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>77</v>
@@ -12195,16 +12047,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>532</v>
+        <v>497</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12223,18 +12073,16 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>379</v>
+        <v>233</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>534</v>
+        <v>267</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>77</v>
       </c>
@@ -12282,25 +12130,25 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>408</v>
+        <v>269</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -12311,21 +12159,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>535</v>
+        <v>498</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>77</v>
@@ -12337,15 +12185,17 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -12394,19 +12244,19 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
@@ -12423,14 +12273,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>536</v>
+        <v>499</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12443,24 +12293,26 @@
         <v>77</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>272</v>
+        <v>389</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
       </c>
@@ -12508,7 +12360,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>276</v>
+        <v>390</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12526,7 +12378,7 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -12537,45 +12389,45 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>136</v>
+        <v>423</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>142</v>
+        <v>424</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -12600,10 +12452,10 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="Z92" t="s" s="2">
         <v>77</v>
@@ -12624,25 +12476,25 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>130</v>
+        <v>415</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -12653,18 +12505,18 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>420</v>
+        <v>77</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>87</v>
@@ -12679,20 +12531,16 @@
         <v>77</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>421</v>
+        <v>267</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>77</v>
       </c>
@@ -12716,10 +12564,10 @@
         <v>77</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Z93" t="s" s="2">
         <v>77</v>
@@ -12740,10 +12588,10 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>419</v>
+        <v>269</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>87</v>
@@ -12752,13 +12600,13 @@
         <v>77</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -12769,21 +12617,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>539</v>
+        <v>502</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>77</v>
@@ -12795,15 +12643,17 @@
         <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -12840,31 +12690,31 @@
         <v>77</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
@@ -12881,14 +12731,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12904,21 +12754,23 @@
         <v>77</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>133</v>
+        <v>461</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>134</v>
+        <v>462</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>272</v>
+        <v>463</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
       </c>
@@ -12954,19 +12806,19 @@
         <v>77</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>276</v>
+        <v>466</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12978,27 +12830,27 @@
         <v>77</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>270</v>
+        <v>467</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>77</v>
+        <v>468</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>541</v>
+        <v>504</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13009,7 +12861,7 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>77</v>
@@ -13021,19 +12873,19 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>443</v>
+        <v>233</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>77</v>
@@ -13043,7 +12895,7 @@
         <v>77</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>77</v>
+        <v>505</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>77</v>
@@ -13082,13 +12934,13 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>77</v>
@@ -13100,21 +12952,21 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>450</v>
+        <v>478</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>542</v>
+        <v>506</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>500</v>
+        <v>426</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13122,7 +12974,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>87</v>
@@ -13134,23 +12986,19 @@
         <v>77</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>233</v>
+        <v>427</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>501</v>
+        <v>428</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>77</v>
       </c>
@@ -13159,7 +13007,7 @@
         <v>77</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>543</v>
+        <v>77</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>77</v>
@@ -13198,10 +13046,10 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>505</v>
+        <v>426</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>87</v>
@@ -13216,21 +13064,21 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>506</v>
+        <v>415</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>507</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>426</v>
+        <v>507</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13238,10 +13086,10 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>77</v>
@@ -13253,16 +13101,18 @@
         <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>531</v>
+        <v>379</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>428</v>
+        <v>508</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>429</v>
+        <v>509</v>
       </c>
       <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
       </c>
@@ -13310,13 +13160,13 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>426</v>
+        <v>507</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>77</v>
@@ -13339,23 +13189,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>545</v>
+        <v>511</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>77</v>
@@ -13367,18 +13215,16 @@
         <v>77</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>379</v>
+        <v>233</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>547</v>
+        <v>267</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>77</v>
       </c>
@@ -13426,25 +13272,25 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>408</v>
+        <v>269</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
@@ -13455,21 +13301,21 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>548</v>
+        <v>512</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>416</v>
+        <v>512</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>77</v>
@@ -13481,15 +13327,17 @@
         <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -13538,19 +13386,19 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>77</v>
@@ -13567,14 +13415,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>417</v>
+        <v>513</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -13587,24 +13435,26 @@
         <v>77</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>272</v>
+        <v>389</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O101" s="2"/>
+      <c r="O101" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>77</v>
       </c>
@@ -13652,7 +13502,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>276</v>
+        <v>390</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13670,7 +13520,7 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
@@ -13681,45 +13531,43 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>550</v>
+        <v>514</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>418</v>
+        <v>514</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>388</v>
+        <v>515</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>142</v>
+        <v>517</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -13744,10 +13592,10 @@
         <v>77</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>77</v>
+        <v>518</v>
       </c>
       <c r="Z102" t="s" s="2">
         <v>77</v>
@@ -13768,25 +13616,25 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>390</v>
+        <v>514</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>130</v>
+        <v>415</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -13797,14 +13645,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>551</v>
+        <v>519</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>419</v>
+        <v>519</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>420</v>
+        <v>77</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -13823,19 +13671,17 @@
         <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>192</v>
+        <v>427</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>421</v>
+        <v>520</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>424</v>
+        <v>522</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13860,10 +13706,10 @@
         <v>77</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Z103" t="s" s="2">
         <v>77</v>
@@ -13884,7 +13730,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>419</v>
+        <v>519</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>87</v>
@@ -13911,1262 +13757,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="P107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
-      <c r="P110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN114">
+  <autoFilter ref="A1:AN103">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15176,7 +13768,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI113">
+  <conditionalFormatting sqref="A2:AI102">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
